--- a/XLibur.Tests/Resource/Examples/Misc/SheetViews.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/SheetViews.xlsx
@@ -13,6 +13,7 @@
     <x:sheet name="ZoomScaleTooSmall" sheetId="5" r:id="rId6"/>
     <x:sheet name="ZoomScaleTooBig" sheetId="6" r:id="rId7"/>
     <x:sheet name="TopLeftCell" sheetId="7" r:id="rId8"/>
+    <x:sheet name="FocusCell" sheetId="8" r:id="rId9"/>
   </x:sheets>
   <x:definedNames/>
   <x:calcPr calcId="125725"/>
@@ -38,6 +39,12 @@
   </x:si>
   <x:si>
     <x:t>ZoomScaleTooBig</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Frozen header</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Focused row</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -529,4 +536,31 @@
   <x:headerFooter/>
   <x:tableParts count="0"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:A500"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1" spans="1:1">
+      <x:c r="A1" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="500" spans="1:1">
+      <x:c r="A500" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
 </file>